--- a/data/batches/2026-09/send_list.xlsx
+++ b/data/batches/2026-09/send_list.xlsx
@@ -919,454 +919,454 @@
     <t>Zaki Daeng</t>
   </si>
   <si>
-    <t>budi.nugroho337@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.utomo268@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.siregar337@gmail.com</t>
-  </si>
-  <si>
-    <t>fajar.lestari247@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.susanto1@gmail.com</t>
-  </si>
-  <si>
-    <t>kartika.tanjung895@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.setiawan838@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.pratama692@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.sitompul136@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.harahap448@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>dewi.gunawan383@outlook.com</t>
-  </si>
-  <si>
-    <t>gilang.kusuma348@outlook.com</t>
-  </si>
-  <si>
-    <t>irfan.nugroho737@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.permana490@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>joko.susanto358@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung230@outlook.com</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.ramadhan292@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.permana166@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.pratama5@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.santoso185@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.lestari939@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.halim973@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.purnomo235@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>surya.rahayu829@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>andi.pratama829@gmail.com</t>
-  </si>
-  <si>
-    <t>taufik.kusuma643@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.setiawan119@outlook.com</t>
-  </si>
-  <si>
-    <t>surya.harahap93@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>fitri.harahap242@outlook.com</t>
-  </si>
-  <si>
-    <t>hana.susanto763@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.hidayat911@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>putri.tanjung36@gmial.com</t>
-  </si>
-  <si>
-    <t>putri.siregar5@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.setiawan607@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.hakim536@outlook.com</t>
-  </si>
-  <si>
-    <t>eko.tanjung306.old@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.harahap839@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>putri.lestari568@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hendra.gunawan940@gmail.com</t>
-  </si>
-  <si>
-    <t>rina.harahap48@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.nugroho155@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.setiawan655@outlook.com</t>
-  </si>
-  <si>
-    <t>hana.nugroho214@outlook.com</t>
-  </si>
-  <si>
-    <t>utami.rahayu707@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.sitompul456@outlook.com</t>
-  </si>
-  <si>
-    <t>gilang.halim475@outlook.com</t>
-  </si>
-  <si>
-    <t>budi.permana35@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.hakim372@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.santoso192@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.wibowo69@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>joko.hakim562@outlook.com</t>
-  </si>
-  <si>
-    <t>wahyu.permana384@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.sitompul967@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.com</t>
-  </si>
-  <si>
-    <t>surya.wijaya733@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>vina.susanto973@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.pratama94@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.sitompul744@outlook.com</t>
-  </si>
-  <si>
-    <t>tika.firmansyah424@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.nasution839@gmail.com</t>
-  </si>
-  <si>
-    <t>fajar.purnomo953@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.marpaung102@outlook.com</t>
-  </si>
-  <si>
-    <t>eko.marpaung525@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>yuni.pratama110@outlook.com</t>
-  </si>
-  <si>
-    <t>gita.nugroho310@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.pratama295@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.hakim495@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.wijaya211@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.ramadhan266@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>utami.lestari977.old@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>gilang.purnomo421@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.rahayu567@outlook.com; indah.daeng923@outlook.com</t>
-  </si>
-  <si>
-    <t>gita.hidayat136@gmail.com</t>
-  </si>
-  <si>
-    <t>laras.pratama420@outlook.com</t>
-  </si>
-  <si>
-    <t>oki.marpaung169@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>dimas.utomo981@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.simanjuntak940@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>nanda.setiawan155@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.gunawan950@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.santoso755@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>gita.harahap701@outlook.com</t>
-  </si>
-  <si>
-    <t>wahyu.santoso947@outlook.com</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak295@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>indah.sitompul761@outlook.com</t>
-  </si>
-  <si>
-    <t>gita.pane367@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.santoso493@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.hakim660@gmail.com</t>
-  </si>
-  <si>
-    <t>taufik.purnomo473@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.wijaya153@gmail.com</t>
-  </si>
-  <si>
-    <t>oki.harahap19@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.nugroho566@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wulan.ramadhan78@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.daeng504@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wulan.firmansyah542@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>laras.harahap333@gmail.com</t>
-  </si>
-  <si>
-    <t>indah.simanjuntak489@gmail.com</t>
-  </si>
-  <si>
-    <t>budi.firmansyah122@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.saputra534@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.setiawan898@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.saputra601@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.lestari650@gmail.com</t>
-  </si>
-  <si>
-    <t>indah.santoso438@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>mega.tanjung710@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.setiawan761@gmail.com</t>
-  </si>
-  <si>
-    <t>rina.halim222@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.purnomo689@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.saputra440@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.gunawan411@outlook.com</t>
-  </si>
-  <si>
-    <t>agus.gunawan88@outlook.com</t>
-  </si>
-  <si>
-    <t>joko.hakim589@outlook.com</t>
-  </si>
-  <si>
-    <t>tika.gunawan465@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>bayu.simanjuntak308@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hana.sitompul434@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.wijaya532@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.firmansyah508@outlook.com</t>
-  </si>
-  <si>
-    <t>budi.rahayu406@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.permana924@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.com</t>
-  </si>
-  <si>
-    <t>putri.halim333@outlook.com</t>
-  </si>
-  <si>
-    <t>wulan.harahap781@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.pane11@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>bayu.pane802@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.santoso953@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.rahayu804@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.tanjung401@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.lestari850@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>agus.setiawan823@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wulan.halim37@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.susanto703@gmail.com</t>
-  </si>
-  <si>
-    <t>citra.gunawan898@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.harahap213@outlook.com</t>
-  </si>
-  <si>
-    <t>yuni.sitompul220@outlook.com</t>
-  </si>
-  <si>
-    <t>dimas.rahayu793@outlook.com</t>
-  </si>
-  <si>
-    <t>yuni.susanto823@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.gunawan937@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.wijaya940@outlook.com</t>
-  </si>
-  <si>
-    <t>sari.simanjuntak854@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.simanjuntak949@gmail.com</t>
-  </si>
-  <si>
-    <t>nanda.marpaung438@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.harahap1@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.sitompul616@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.susanto514@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.nugroho496@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.halim48@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.permana471@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.hidayat608@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.daeng276@gmail.com</t>
+    <t>budi.nugroho337@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.utomo268@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.siregar337@gmail.example</t>
+  </si>
+  <si>
+    <t>fajar.lestari247@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.susanto1@gmail.example</t>
+  </si>
+  <si>
+    <t>kartika.tanjung895@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.setiawan838@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.pratama692@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.sitompul136@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.harahap448@yahoo.example</t>
+  </si>
+  <si>
+    <t>dewi.gunawan383@outlook.example</t>
+  </si>
+  <si>
+    <t>gilang.kusuma348@outlook.example</t>
+  </si>
+  <si>
+    <t>irfan.nugroho737@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.permana490@yahoo.example</t>
+  </si>
+  <si>
+    <t>joko.susanto358@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.marpaung230@outlook.example</t>
+  </si>
+  <si>
+    <t>mega.syahputra515@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.ramadhan292@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.permana166@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.pratama5@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.santoso185@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.lestari939@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.halim973@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.purnomo235@yahoo.example</t>
+  </si>
+  <si>
+    <t>surya.rahayu829@yahoo.example</t>
+  </si>
+  <si>
+    <t>andi.pratama829@gmail.example</t>
+  </si>
+  <si>
+    <t>taufik.kusuma643@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.setiawan119@outlook.example</t>
+  </si>
+  <si>
+    <t>surya.harahap93@yahoo.example</t>
+  </si>
+  <si>
+    <t>fitri.harahap242@outlook.example</t>
+  </si>
+  <si>
+    <t>hana.susanto763@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.hidayat911@yahoo.example</t>
+  </si>
+  <si>
+    <t>putri.tanjung36@gmial.example</t>
+  </si>
+  <si>
+    <t>putri.siregar5@yahoo.example</t>
+  </si>
+  <si>
+    <t>sari.nasution814@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.setiawan607@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.hakim536@outlook.example</t>
+  </si>
+  <si>
+    <t>eko.tanjung306.old@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.harahap839@yahoo.example</t>
+  </si>
+  <si>
+    <t>putri.lestari568@yahoo.example</t>
+  </si>
+  <si>
+    <t>hendra.gunawan940@gmail.example</t>
+  </si>
+  <si>
+    <t>rina.harahap48@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.nugroho155@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.setiawan655@outlook.example</t>
+  </si>
+  <si>
+    <t>hana.nugroho214@outlook.example</t>
+  </si>
+  <si>
+    <t>utami.rahayu707@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.sitompul456@outlook.example</t>
+  </si>
+  <si>
+    <t>gilang.halim475@outlook.example</t>
+  </si>
+  <si>
+    <t>budi.permana35@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.hakim372@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.santoso192@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.wibowo69@yahoo.example</t>
+  </si>
+  <si>
+    <t>joko.hakim562@outlook.example</t>
+  </si>
+  <si>
+    <t>wahyu.permana384@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.sitompul967@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.simanjuntak858@gmail.example</t>
+  </si>
+  <si>
+    <t>surya.wijaya733@yahoo.example</t>
+  </si>
+  <si>
+    <t>vina.susanto973@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.pratama94@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.sitompul744@outlook.example</t>
+  </si>
+  <si>
+    <t>tika.firmansyah424@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.nasution839@gmail.example</t>
+  </si>
+  <si>
+    <t>fajar.purnomo953@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.marpaung102@outlook.example</t>
+  </si>
+  <si>
+    <t>eko.marpaung525@yahoo.example</t>
+  </si>
+  <si>
+    <t>yuni.pratama110@outlook.example</t>
+  </si>
+  <si>
+    <t>gita.nugroho310@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.pratama295@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.hakim495@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.wijaya211@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.ramadhan266@yahoo.example</t>
+  </si>
+  <si>
+    <t>utami.lestari977.old@yahoo.example</t>
+  </si>
+  <si>
+    <t>gilang.purnomo421@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.rahayu567@outlook.example; indah.daeng923@outlook.example</t>
+  </si>
+  <si>
+    <t>gita.hidayat136@gmail.example</t>
+  </si>
+  <si>
+    <t>laras.pratama420@outlook.example</t>
+  </si>
+  <si>
+    <t>oki.marpaung169@yahoo.example</t>
+  </si>
+  <si>
+    <t>dimas.utomo981@yahoo.example</t>
+  </si>
+  <si>
+    <t>wahyu.tanjung859@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.simanjuntak940@yahoo.example</t>
+  </si>
+  <si>
+    <t>nanda.setiawan155@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.gunawan950@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.santoso755@yahoo.example</t>
+  </si>
+  <si>
+    <t>gita.harahap701@outlook.example</t>
+  </si>
+  <si>
+    <t>wahyu.santoso947@outlook.example</t>
+  </si>
+  <si>
+    <t>dewi.simanjuntak295@yahoo.example</t>
+  </si>
+  <si>
+    <t>indah.sitompul761@outlook.example</t>
+  </si>
+  <si>
+    <t>gita.pane367@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.santoso493@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.hakim660@gmail.example</t>
+  </si>
+  <si>
+    <t>taufik.purnomo473@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.wijaya153@gmail.example</t>
+  </si>
+  <si>
+    <t>oki.harahap19@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.nugroho566@yahoo.example</t>
+  </si>
+  <si>
+    <t>wulan.ramadhan78@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.daeng504@yahoo.example</t>
+  </si>
+  <si>
+    <t>wulan.firmansyah542@yahoo.example</t>
+  </si>
+  <si>
+    <t>laras.harahap333@gmail.example</t>
+  </si>
+  <si>
+    <t>indah.simanjuntak489@gmail.example</t>
+  </si>
+  <si>
+    <t>budi.firmansyah122@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.saputra534@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.setiawan898@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.saputra601@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.lestari650@gmail.example</t>
+  </si>
+  <si>
+    <t>indah.santoso438@yahoo.example</t>
+  </si>
+  <si>
+    <t>mega.tanjung710@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.setiawan761@gmail.example</t>
+  </si>
+  <si>
+    <t>rina.halim222@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.purnomo689@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.saputra440@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.gunawan411@outlook.example</t>
+  </si>
+  <si>
+    <t>agus.gunawan88@outlook.example</t>
+  </si>
+  <si>
+    <t>joko.hakim589@outlook.example</t>
+  </si>
+  <si>
+    <t>tika.gunawan465@yahoo.example</t>
+  </si>
+  <si>
+    <t>bayu.simanjuntak308@yahoo.example</t>
+  </si>
+  <si>
+    <t>hana.sitompul434@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.wijaya532@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.firmansyah508@outlook.example</t>
+  </si>
+  <si>
+    <t>budi.rahayu406@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.permana924@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.rahayu13@outlook.example</t>
+  </si>
+  <si>
+    <t>putri.halim333@outlook.example</t>
+  </si>
+  <si>
+    <t>wulan.harahap781@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.pane11@yahoo.example</t>
+  </si>
+  <si>
+    <t>bayu.pane802@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.santoso953@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.rahayu804@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.tanjung401@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.lestari850@yahoo.example</t>
+  </si>
+  <si>
+    <t>agus.setiawan823@yahoo.example</t>
+  </si>
+  <si>
+    <t>wulan.halim37@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.susanto703@gmail.example</t>
+  </si>
+  <si>
+    <t>citra.gunawan898@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.harahap213@outlook.example</t>
+  </si>
+  <si>
+    <t>yuni.sitompul220@outlook.example</t>
+  </si>
+  <si>
+    <t>dimas.rahayu793@outlook.example</t>
+  </si>
+  <si>
+    <t>yuni.susanto823@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.gunawan937@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.wijaya940@outlook.example</t>
+  </si>
+  <si>
+    <t>sari.simanjuntak854@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.simanjuntak949@gmail.example</t>
+  </si>
+  <si>
+    <t>nanda.marpaung438@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.harahap1@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.sitompul616@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.susanto514@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.nugroho496@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.halim48@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.permana471@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.hidayat608@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.daeng276@gmail.example</t>
   </si>
   <si>
     <t>MDN</t>
@@ -1396,7 +1396,7 @@
     <t>REINSTATEMENT</t>
   </si>
   <si>
-    <t>jkt.staff@gmail.com</t>
+    <t>jkt.staff@gmail.example</t>
   </si>
 </sst>
 </file>

--- a/data/batches/2026-09/send_list.xlsx
+++ b/data/batches/2026-09/send_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="451">
   <si>
     <t>batch_id</t>
   </si>
@@ -40,1363 +40,1333 @@
     <t>2026-09</t>
   </si>
   <si>
-    <t>7724184637</t>
-  </si>
-  <si>
-    <t>7787831446</t>
-  </si>
-  <si>
-    <t>7794744011</t>
-  </si>
-  <si>
-    <t>7727198217</t>
-  </si>
-  <si>
-    <t>7794938397</t>
-  </si>
-  <si>
-    <t>7756646959</t>
-  </si>
-  <si>
-    <t>7707975643</t>
-  </si>
-  <si>
-    <t>7721524102</t>
-  </si>
-  <si>
-    <t>7753993392</t>
-  </si>
-  <si>
-    <t>7704350243</t>
-  </si>
-  <si>
-    <t>7726985678</t>
-  </si>
-  <si>
-    <t>7772720029</t>
-  </si>
-  <si>
-    <t>7761094723</t>
-  </si>
-  <si>
-    <t>7736995674</t>
-  </si>
-  <si>
-    <t>7719031847</t>
-  </si>
-  <si>
-    <t>7792954364</t>
-  </si>
-  <si>
-    <t>7798227701</t>
-  </si>
-  <si>
-    <t>7774524337</t>
-  </si>
-  <si>
-    <t>7754432040</t>
-  </si>
-  <si>
-    <t>7729329462</t>
-  </si>
-  <si>
-    <t>7701559388</t>
-  </si>
-  <si>
-    <t>7735103073</t>
-  </si>
-  <si>
-    <t>7725663794</t>
-  </si>
-  <si>
-    <t>7724696916</t>
-  </si>
-  <si>
-    <t>7751102763</t>
-  </si>
-  <si>
-    <t>7715838345</t>
-  </si>
-  <si>
-    <t>7733658049</t>
-  </si>
-  <si>
-    <t>7771395719</t>
-  </si>
-  <si>
-    <t>7721699095</t>
-  </si>
-  <si>
-    <t>7789780271</t>
-  </si>
-  <si>
-    <t>7717262909</t>
-  </si>
-  <si>
-    <t>7746964069</t>
-  </si>
-  <si>
-    <t>7751164647</t>
-  </si>
-  <si>
-    <t>7742937678</t>
-  </si>
-  <si>
-    <t>7748432235</t>
-  </si>
-  <si>
-    <t>7768749581</t>
-  </si>
-  <si>
-    <t>7752861743</t>
-  </si>
-  <si>
-    <t>7710321322</t>
-  </si>
-  <si>
-    <t>7730286979</t>
-  </si>
-  <si>
-    <t>7759675119</t>
-  </si>
-  <si>
-    <t>7780477117</t>
-  </si>
-  <si>
-    <t>7727221816</t>
-  </si>
-  <si>
-    <t>7782617476</t>
-  </si>
-  <si>
-    <t>7783297898</t>
-  </si>
-  <si>
-    <t>7791719686</t>
-  </si>
-  <si>
-    <t>7769782512</t>
-  </si>
-  <si>
-    <t>7701319280</t>
-  </si>
-  <si>
-    <t>7700813433</t>
-  </si>
-  <si>
-    <t>7792887665</t>
-  </si>
-  <si>
-    <t>7724071994</t>
-  </si>
-  <si>
-    <t>7773289551</t>
-  </si>
-  <si>
-    <t>7719903641</t>
-  </si>
-  <si>
-    <t>7767795062</t>
-  </si>
-  <si>
-    <t>7763280819</t>
-  </si>
-  <si>
-    <t>7789276147</t>
-  </si>
-  <si>
-    <t>7707449684</t>
-  </si>
-  <si>
-    <t>7735914275</t>
-  </si>
-  <si>
-    <t>7734285995</t>
-  </si>
-  <si>
-    <t>7733170715</t>
-  </si>
-  <si>
-    <t>7721151267</t>
-  </si>
-  <si>
-    <t>7788176101</t>
-  </si>
-  <si>
-    <t>7793364709</t>
-  </si>
-  <si>
-    <t>7744923879</t>
-  </si>
-  <si>
-    <t>7771432954</t>
-  </si>
-  <si>
-    <t>7757965484</t>
-  </si>
-  <si>
-    <t>7750165584</t>
-  </si>
-  <si>
-    <t>7795577864</t>
-  </si>
-  <si>
-    <t>7796810185</t>
-  </si>
-  <si>
-    <t>7726474594</t>
-  </si>
-  <si>
-    <t>7729294816</t>
-  </si>
-  <si>
-    <t>7760938246</t>
-  </si>
-  <si>
-    <t>7783839028</t>
-  </si>
-  <si>
-    <t>7766276407</t>
-  </si>
-  <si>
-    <t>7706342956</t>
-  </si>
-  <si>
-    <t>7734983146</t>
-  </si>
-  <si>
-    <t>7744096577</t>
-  </si>
-  <si>
-    <t>7775312124</t>
-  </si>
-  <si>
-    <t>7702044419</t>
-  </si>
-  <si>
-    <t>7797690923</t>
-  </si>
-  <si>
-    <t>7757479159</t>
-  </si>
-  <si>
-    <t>7788862381</t>
-  </si>
-  <si>
-    <t>7792721592</t>
-  </si>
-  <si>
-    <t>7757844933</t>
-  </si>
-  <si>
-    <t>7731387065</t>
-  </si>
-  <si>
-    <t>7718087769</t>
-  </si>
-  <si>
-    <t>7729011601</t>
-  </si>
-  <si>
-    <t>7755187908</t>
-  </si>
-  <si>
-    <t>7796676843</t>
-  </si>
-  <si>
-    <t>7748459262</t>
-  </si>
-  <si>
-    <t>7764327521</t>
-  </si>
-  <si>
-    <t>7763643347</t>
-  </si>
-  <si>
-    <t>7758913982</t>
-  </si>
-  <si>
-    <t>7757426050</t>
-  </si>
-  <si>
-    <t>7789227581</t>
+    <t>7773965956</t>
+  </si>
+  <si>
+    <t>7776811052</t>
+  </si>
+  <si>
+    <t>7706429168</t>
+  </si>
+  <si>
+    <t>7706870732</t>
+  </si>
+  <si>
+    <t>7753455308</t>
+  </si>
+  <si>
+    <t>7746604513</t>
+  </si>
+  <si>
+    <t>7731763333</t>
+  </si>
+  <si>
+    <t>7733423885</t>
+  </si>
+  <si>
+    <t>7738367669</t>
+  </si>
+  <si>
+    <t>7756713665</t>
+  </si>
+  <si>
+    <t>7789264626</t>
+  </si>
+  <si>
+    <t>7706204465</t>
+  </si>
+  <si>
+    <t>7769363640</t>
+  </si>
+  <si>
+    <t>7709200787</t>
+  </si>
+  <si>
+    <t>7734013978</t>
+  </si>
+  <si>
+    <t>7761678333</t>
+  </si>
+  <si>
+    <t>7768280244</t>
+  </si>
+  <si>
+    <t>7711561837</t>
+  </si>
+  <si>
+    <t>7780705467</t>
+  </si>
+  <si>
+    <t>7798540613</t>
+  </si>
+  <si>
+    <t>7732561133</t>
+  </si>
+  <si>
+    <t>7772716655</t>
+  </si>
+  <si>
+    <t>7797064739</t>
+  </si>
+  <si>
+    <t>7761642926</t>
+  </si>
+  <si>
+    <t>7786284849</t>
+  </si>
+  <si>
+    <t>7769999878</t>
+  </si>
+  <si>
+    <t>7743272579</t>
+  </si>
+  <si>
+    <t>7787700527</t>
+  </si>
+  <si>
+    <t>7715184002</t>
+  </si>
+  <si>
+    <t>7732829520</t>
+  </si>
+  <si>
+    <t>7739250179</t>
+  </si>
+  <si>
+    <t>7734092651</t>
+  </si>
+  <si>
+    <t>7704269797</t>
+  </si>
+  <si>
+    <t>7753176456</t>
+  </si>
+  <si>
+    <t>7739627503</t>
+  </si>
+  <si>
+    <t>7700233103</t>
+  </si>
+  <si>
+    <t>7718894612</t>
+  </si>
+  <si>
+    <t>7784406856</t>
+  </si>
+  <si>
+    <t>7716937981</t>
+  </si>
+  <si>
+    <t>7720709724</t>
+  </si>
+  <si>
+    <t>7748557282</t>
+  </si>
+  <si>
+    <t>7704917079</t>
+  </si>
+  <si>
+    <t>7720546494</t>
+  </si>
+  <si>
+    <t>7764357565</t>
+  </si>
+  <si>
+    <t>7735153476</t>
+  </si>
+  <si>
+    <t>7700551619</t>
+  </si>
+  <si>
+    <t>7719288385</t>
+  </si>
+  <si>
+    <t>7704673581</t>
+  </si>
+  <si>
+    <t>7749519807</t>
+  </si>
+  <si>
+    <t>7762946999</t>
+  </si>
+  <si>
+    <t>7778645999</t>
+  </si>
+  <si>
+    <t>7704818170</t>
+  </si>
+  <si>
+    <t>7713342500</t>
+  </si>
+  <si>
+    <t>7747114725</t>
+  </si>
+  <si>
+    <t>7758916018</t>
+  </si>
+  <si>
+    <t>7792070437</t>
+  </si>
+  <si>
+    <t>7791407954</t>
+  </si>
+  <si>
+    <t>7734210904</t>
+  </si>
+  <si>
+    <t>7799761938</t>
+  </si>
+  <si>
+    <t>7755232332</t>
+  </si>
+  <si>
+    <t>7751949385</t>
+  </si>
+  <si>
+    <t>7731005775</t>
+  </si>
+  <si>
+    <t>7701003907</t>
+  </si>
+  <si>
+    <t>7779166963</t>
+  </si>
+  <si>
+    <t>7787302117</t>
+  </si>
+  <si>
+    <t>7709516605</t>
+  </si>
+  <si>
+    <t>7709272279</t>
+  </si>
+  <si>
+    <t>7787171057</t>
+  </si>
+  <si>
+    <t>7781089846</t>
+  </si>
+  <si>
+    <t>7745934227</t>
+  </si>
+  <si>
+    <t>7747987189</t>
+  </si>
+  <si>
+    <t>7715243183</t>
+  </si>
+  <si>
+    <t>7797216942</t>
+  </si>
+  <si>
+    <t>7754928292</t>
+  </si>
+  <si>
+    <t>7714254603</t>
+  </si>
+  <si>
+    <t>7726242028</t>
+  </si>
+  <si>
+    <t>7715126130</t>
+  </si>
+  <si>
+    <t>7751182194</t>
+  </si>
+  <si>
+    <t>7761078678</t>
+  </si>
+  <si>
+    <t>7790542559</t>
+  </si>
+  <si>
+    <t>7773075794</t>
+  </si>
+  <si>
+    <t>7793610579</t>
+  </si>
+  <si>
+    <t>7757688669</t>
+  </si>
+  <si>
+    <t>7725955055</t>
+  </si>
+  <si>
+    <t>7728750039</t>
+  </si>
+  <si>
+    <t>7743335070</t>
+  </si>
+  <si>
+    <t>7771997585</t>
+  </si>
+  <si>
+    <t>7747657240</t>
+  </si>
+  <si>
+    <t>7729915890</t>
+  </si>
+  <si>
+    <t>7706162073</t>
+  </si>
+  <si>
+    <t>7718917928</t>
+  </si>
+  <si>
+    <t>7756245449</t>
+  </si>
+  <si>
+    <t>7747385578</t>
+  </si>
+  <si>
+    <t>7788143897</t>
+  </si>
+  <si>
+    <t>7793154277</t>
+  </si>
+  <si>
+    <t>7763037495</t>
+  </si>
+  <si>
+    <t>7707782831</t>
+  </si>
+  <si>
+    <t>7721226939</t>
+  </si>
+  <si>
+    <t>7720450247</t>
+  </si>
+  <si>
+    <t>7793154748</t>
+  </si>
+  <si>
+    <t>7782011040</t>
+  </si>
+  <si>
+    <t>7758558155</t>
+  </si>
+  <si>
+    <t>7709086971</t>
+  </si>
+  <si>
+    <t>7790379502</t>
+  </si>
+  <si>
+    <t>7761478244</t>
+  </si>
+  <si>
+    <t>7717874442</t>
+  </si>
+  <si>
+    <t>7718388676</t>
+  </si>
+  <si>
+    <t>7727260710</t>
+  </si>
+  <si>
+    <t>7779815661</t>
+  </si>
+  <si>
+    <t>7785828392</t>
+  </si>
+  <si>
+    <t>7791237918</t>
+  </si>
+  <si>
+    <t>7774764247</t>
+  </si>
+  <si>
+    <t>7714090496</t>
+  </si>
+  <si>
+    <t>7735509484</t>
+  </si>
+  <si>
+    <t>7778508550</t>
+  </si>
+  <si>
+    <t>7737801615</t>
+  </si>
+  <si>
+    <t>7731433948</t>
+  </si>
+  <si>
+    <t>7731093920</t>
+  </si>
+  <si>
+    <t>7700888043</t>
+  </si>
+  <si>
+    <t>7722645319</t>
+  </si>
+  <si>
+    <t>7709630566</t>
+  </si>
+  <si>
+    <t>7700155678</t>
+  </si>
+  <si>
+    <t>7706761712</t>
+  </si>
+  <si>
+    <t>7750592607</t>
+  </si>
+  <si>
+    <t>7790011378</t>
+  </si>
+  <si>
+    <t>7759600584</t>
+  </si>
+  <si>
+    <t>7760787811</t>
+  </si>
+  <si>
+    <t>7769498984</t>
+  </si>
+  <si>
+    <t>7774495413</t>
+  </si>
+  <si>
+    <t>7749836305</t>
+  </si>
+  <si>
+    <t>7754611265</t>
+  </si>
+  <si>
+    <t>7746473336</t>
+  </si>
+  <si>
+    <t>7778865078</t>
+  </si>
+  <si>
+    <t>7779441142</t>
+  </si>
+  <si>
+    <t>7799751309</t>
+  </si>
+  <si>
+    <t>7716650857</t>
+  </si>
+  <si>
+    <t>7725825686</t>
+  </si>
+  <si>
+    <t>7789788468</t>
+  </si>
+  <si>
+    <t>7731296980</t>
+  </si>
+  <si>
+    <t>7712699625</t>
+  </si>
+  <si>
+    <t>7755292405</t>
+  </si>
+  <si>
+    <t>7728534732</t>
+  </si>
+  <si>
+    <t>7720403813</t>
+  </si>
+  <si>
+    <t>7741709984</t>
+  </si>
+  <si>
+    <t>7726243555</t>
+  </si>
+  <si>
+    <t>7775971135</t>
+  </si>
+  <si>
+    <t>7779501978</t>
+  </si>
+  <si>
+    <t>7786856586</t>
   </si>
   <si>
     <t>7705357930</t>
   </si>
   <si>
-    <t>7740791374</t>
-  </si>
-  <si>
-    <t>7789283869</t>
-  </si>
-  <si>
-    <t>7732996691</t>
-  </si>
-  <si>
-    <t>7795755765</t>
-  </si>
-  <si>
-    <t>7767328196</t>
-  </si>
-  <si>
-    <t>7766929094</t>
-  </si>
-  <si>
-    <t>7705233061</t>
-  </si>
-  <si>
-    <t>7748460167</t>
-  </si>
-  <si>
-    <t>7727134379</t>
-  </si>
-  <si>
-    <t>7760408941</t>
-  </si>
-  <si>
-    <t>7778128058</t>
-  </si>
-  <si>
-    <t>7754191620</t>
-  </si>
-  <si>
-    <t>7755882486</t>
-  </si>
-  <si>
-    <t>7750107172</t>
-  </si>
-  <si>
-    <t>7720950243</t>
-  </si>
-  <si>
-    <t>7732156288</t>
-  </si>
-  <si>
-    <t>7722280479</t>
-  </si>
-  <si>
-    <t>7722760054</t>
-  </si>
-  <si>
-    <t>7721845383</t>
-  </si>
-  <si>
-    <t>7765959213</t>
-  </si>
-  <si>
-    <t>7746601976</t>
-  </si>
-  <si>
-    <t>7776687553</t>
-  </si>
-  <si>
-    <t>7761058417</t>
-  </si>
-  <si>
-    <t>7789678047</t>
-  </si>
-  <si>
-    <t>7783722273</t>
-  </si>
-  <si>
-    <t>7786367442</t>
-  </si>
-  <si>
-    <t>7796323595</t>
-  </si>
-  <si>
-    <t>7713064856</t>
-  </si>
-  <si>
-    <t>7755421665</t>
-  </si>
-  <si>
-    <t>7722925718</t>
-  </si>
-  <si>
-    <t>7799810789</t>
-  </si>
-  <si>
-    <t>7743274151</t>
-  </si>
-  <si>
-    <t>7727267114</t>
-  </si>
-  <si>
-    <t>7736781978</t>
-  </si>
-  <si>
-    <t>7718002182</t>
-  </si>
-  <si>
-    <t>7792619248</t>
-  </si>
-  <si>
-    <t>7780613914</t>
-  </si>
-  <si>
-    <t>7726102929</t>
-  </si>
-  <si>
-    <t>7762946999</t>
-  </si>
-  <si>
-    <t>7785741202</t>
-  </si>
-  <si>
-    <t>7757369828</t>
-  </si>
-  <si>
-    <t>7751741412</t>
-  </si>
-  <si>
-    <t>7764078431</t>
-  </si>
-  <si>
-    <t>7787018787</t>
-  </si>
-  <si>
-    <t>7747091075</t>
-  </si>
-  <si>
-    <t>7714636196</t>
-  </si>
-  <si>
-    <t>7732055405</t>
-  </si>
-  <si>
-    <t>7793921001</t>
-  </si>
-  <si>
-    <t>7763698778</t>
-  </si>
-  <si>
-    <t>7779905276</t>
-  </si>
-  <si>
-    <t>7751386454</t>
-  </si>
-  <si>
-    <t>7749821866</t>
-  </si>
-  <si>
-    <t>7748684675</t>
-  </si>
-  <si>
-    <t>7748137785</t>
-  </si>
-  <si>
-    <t>7791629695</t>
-  </si>
-  <si>
-    <t>Budi Nugroho</t>
-  </si>
-  <si>
-    <t>Fitri Utomo</t>
-  </si>
-  <si>
-    <t>Rahmat Siregar</t>
-  </si>
-  <si>
-    <t>Fajar Lestari</t>
-  </si>
-  <si>
-    <t>Zaki Susanto</t>
-  </si>
-  <si>
-    <t>Kartika Tanjung</t>
-  </si>
-  <si>
-    <t>Yoga Setiawan</t>
-  </si>
-  <si>
-    <t>Irfan Pratama</t>
-  </si>
-  <si>
-    <t>Fitri Sitompul</t>
-  </si>
-  <si>
-    <t>Rizky Harahap</t>
-  </si>
-  <si>
-    <t>Dewi Gunawan</t>
-  </si>
-  <si>
-    <t>Gilang Kusuma</t>
-  </si>
-  <si>
-    <t>Irfan Nugroho</t>
-  </si>
-  <si>
-    <t>Vina Permana</t>
-  </si>
-  <si>
-    <t>Joko Susanto</t>
-  </si>
-  <si>
-    <t>Wahyu Marpaung</t>
-  </si>
-  <si>
-    <t>Mega Syahputra</t>
-  </si>
-  <si>
-    <t>Dewi Ramadhan</t>
-  </si>
-  <si>
-    <t>Eko Permana</t>
-  </si>
-  <si>
-    <t>Mega Pratama</t>
-  </si>
-  <si>
-    <t>Andi Santoso</t>
-  </si>
-  <si>
-    <t>Irfan Lestari</t>
-  </si>
-  <si>
-    <t>Dimas Halim</t>
-  </si>
-  <si>
-    <t>Fitri Purnomo</t>
-  </si>
-  <si>
-    <t>Surya Rahayu</t>
-  </si>
-  <si>
-    <t>Andi Pratama</t>
-  </si>
-  <si>
-    <t>Taufik Kusuma</t>
-  </si>
-  <si>
-    <t>Fitri Setiawan</t>
-  </si>
-  <si>
-    <t>Surya Harahap</t>
-  </si>
-  <si>
-    <t>Fitri Harahap</t>
-  </si>
-  <si>
-    <t>Hana Susanto</t>
-  </si>
-  <si>
-    <t>Joko Hidayat</t>
-  </si>
-  <si>
-    <t>Putri Tanjung</t>
-  </si>
-  <si>
-    <t>Putri Siregar</t>
-  </si>
-  <si>
-    <t>Sari Nasution</t>
-  </si>
-  <si>
-    <t>Bayu Setiawan</t>
-  </si>
-  <si>
-    <t>Andi Hakim</t>
-  </si>
-  <si>
-    <t>Eko Tanjung</t>
-  </si>
-  <si>
-    <t>Lestari Harahap</t>
-  </si>
-  <si>
-    <t>Putri Lestari</t>
-  </si>
-  <si>
-    <t>Hendra Gunawan</t>
-  </si>
-  <si>
-    <t>Rina Harahap</t>
-  </si>
-  <si>
-    <t>Putri Nugroho</t>
-  </si>
-  <si>
-    <t>Vina Setiawan</t>
-  </si>
-  <si>
-    <t>Hana Nugroho</t>
-  </si>
-  <si>
-    <t>Utami Rahayu</t>
-  </si>
-  <si>
-    <t>Hana Sitompul</t>
-  </si>
-  <si>
-    <t>Gilang Halim</t>
-  </si>
-  <si>
-    <t>Budi Permana</t>
-  </si>
-  <si>
-    <t>Agus Hakim</t>
-  </si>
-  <si>
-    <t>Utami Santoso</t>
-  </si>
-  <si>
-    <t>Lestari Wibowo</t>
-  </si>
-  <si>
-    <t>Joko Hakim</t>
-  </si>
-  <si>
-    <t>Wahyu Permana</t>
-  </si>
-  <si>
-    <t>Dewi Simanjuntak</t>
-  </si>
-  <si>
-    <t>Surya Wijaya</t>
-  </si>
-  <si>
-    <t>Vina Susanto</t>
-  </si>
-  <si>
-    <t>Rizky Pratama</t>
-  </si>
-  <si>
-    <t>Mega Sitompul</t>
-  </si>
-  <si>
-    <t>Tika Firmansyah</t>
-  </si>
-  <si>
-    <t>Nur Nasution</t>
-  </si>
-  <si>
-    <t>Fajar Purnomo</t>
-  </si>
-  <si>
-    <t>Rahmat Marpaung</t>
-  </si>
-  <si>
-    <t>Eko Marpaung</t>
-  </si>
-  <si>
-    <t>Yuni Pratama</t>
-  </si>
-  <si>
-    <t>Gita Nugroho</t>
-  </si>
-  <si>
-    <t>Dewi Pratama</t>
-  </si>
-  <si>
-    <t>Dimas Hakim</t>
-  </si>
-  <si>
-    <t>Hana Wijaya</t>
-  </si>
-  <si>
-    <t>Vina Ramadhan</t>
-  </si>
-  <si>
-    <t>Utami Lestari</t>
-  </si>
-  <si>
-    <t>Gilang Purnomo</t>
-  </si>
-  <si>
-    <t>Gilang Rahayu</t>
-  </si>
-  <si>
-    <t>Gita Hidayat</t>
-  </si>
-  <si>
-    <t>Laras Pratama</t>
-  </si>
-  <si>
-    <t>Oki Marpaung</t>
-  </si>
-  <si>
-    <t>Dimas Utomo</t>
-  </si>
-  <si>
-    <t>Wahyu Tanjung</t>
-  </si>
-  <si>
-    <t>Putri Simanjuntak</t>
-  </si>
-  <si>
-    <t>Nanda Setiawan</t>
-  </si>
-  <si>
-    <t>Gita Gunawan</t>
-  </si>
-  <si>
-    <t>Sari Santoso</t>
-  </si>
-  <si>
-    <t>Gita Harahap</t>
-  </si>
-  <si>
-    <t>Wahyu Santoso</t>
-  </si>
-  <si>
-    <t>Indah Sitompul</t>
-  </si>
-  <si>
-    <t>Gita Pane</t>
-  </si>
-  <si>
-    <t>Putri Santoso</t>
-  </si>
-  <si>
-    <t>Bayu Hakim</t>
-  </si>
-  <si>
-    <t>Taufik Purnomo</t>
-  </si>
-  <si>
-    <t>Gita Wijaya</t>
-  </si>
-  <si>
-    <t>Oki Harahap</t>
-  </si>
-  <si>
-    <t>Gilang Nugroho</t>
-  </si>
-  <si>
-    <t>Wulan Ramadhan</t>
-  </si>
-  <si>
-    <t>Rizky Daeng</t>
-  </si>
-  <si>
-    <t>Wulan Firmansyah</t>
-  </si>
-  <si>
-    <t>Laras Harahap</t>
-  </si>
-  <si>
-    <t>Indah Simanjuntak</t>
-  </si>
-  <si>
-    <t>Budi Firmansyah</t>
-  </si>
-  <si>
-    <t>Utami Saputra</t>
-  </si>
-  <si>
-    <t>Zaki Setiawan</t>
-  </si>
-  <si>
-    <t>Dimas Saputra</t>
-  </si>
-  <si>
-    <t>Nur Lestari</t>
-  </si>
-  <si>
-    <t>Indah Santoso</t>
-  </si>
-  <si>
-    <t>Mega Tanjung</t>
-  </si>
-  <si>
-    <t>Rina Halim</t>
-  </si>
-  <si>
-    <t>Sari Purnomo</t>
-  </si>
-  <si>
-    <t>Andi Saputra</t>
-  </si>
-  <si>
-    <t>Zaki Gunawan</t>
-  </si>
-  <si>
-    <t>Agus Gunawan</t>
-  </si>
-  <si>
-    <t>Tika Gunawan</t>
-  </si>
-  <si>
-    <t>Bayu Simanjuntak</t>
-  </si>
-  <si>
-    <t>Eko Wijaya</t>
-  </si>
-  <si>
-    <t>Hana Firmansyah</t>
-  </si>
-  <si>
-    <t>Budi Rahayu</t>
-  </si>
-  <si>
-    <t>Fitri Rahayu</t>
-  </si>
-  <si>
-    <t>Putri Halim</t>
-  </si>
-  <si>
-    <t>Wulan Harahap</t>
-  </si>
-  <si>
-    <t>Andi Pane</t>
-  </si>
-  <si>
-    <t>Bayu Pane</t>
-  </si>
-  <si>
-    <t>Nur Santoso</t>
-  </si>
-  <si>
-    <t>Eko Rahayu</t>
-  </si>
-  <si>
-    <t>Lestari Tanjung</t>
-  </si>
-  <si>
-    <t>Wulan Lestari</t>
-  </si>
-  <si>
-    <t>Agus Setiawan</t>
-  </si>
-  <si>
-    <t>Wulan Halim</t>
-  </si>
-  <si>
-    <t>Dimas Susanto</t>
-  </si>
-  <si>
-    <t>Citra Gunawan</t>
-  </si>
-  <si>
-    <t>Agus Harahap</t>
-  </si>
-  <si>
-    <t>Yuni Sitompul</t>
-  </si>
-  <si>
-    <t>Dimas Rahayu</t>
-  </si>
-  <si>
-    <t>Yuni Susanto</t>
-  </si>
-  <si>
-    <t>Gilang Gunawan</t>
-  </si>
-  <si>
-    <t>Andi Wijaya</t>
-  </si>
-  <si>
-    <t>Sari Simanjuntak</t>
-  </si>
-  <si>
-    <t>Eko Simanjuntak</t>
-  </si>
-  <si>
-    <t>Nanda Marpaung</t>
-  </si>
-  <si>
-    <t>Dimas Harahap</t>
-  </si>
-  <si>
-    <t>Utami Sitompul</t>
-  </si>
-  <si>
-    <t>Wahyu Susanto</t>
-  </si>
-  <si>
-    <t>Vina Nugroho</t>
-  </si>
-  <si>
-    <t>Gilang Permana</t>
-  </si>
-  <si>
-    <t>Dewi Hidayat</t>
-  </si>
-  <si>
-    <t>Zaki Daeng</t>
-  </si>
-  <si>
-    <t>budi.nugroho337@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.utomo268@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.siregar337@gmail.example</t>
-  </si>
-  <si>
-    <t>fajar.lestari247@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.susanto1@gmail.example</t>
-  </si>
-  <si>
-    <t>kartika.tanjung895@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.setiawan838@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.pratama692@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.sitompul136@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.harahap448@yahoo.example</t>
-  </si>
-  <si>
-    <t>dewi.gunawan383@outlook.example</t>
-  </si>
-  <si>
-    <t>gilang.kusuma348@outlook.example</t>
-  </si>
-  <si>
-    <t>irfan.nugroho737@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.permana490@yahoo.example</t>
-  </si>
-  <si>
-    <t>joko.susanto358@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung230@outlook.example</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.ramadhan292@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.permana166@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.pratama5@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.santoso185@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.lestari939@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.halim973@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.purnomo235@yahoo.example</t>
-  </si>
-  <si>
-    <t>surya.rahayu829@yahoo.example</t>
-  </si>
-  <si>
-    <t>andi.pratama829@gmail.example</t>
-  </si>
-  <si>
-    <t>taufik.kusuma643@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.setiawan119@outlook.example</t>
-  </si>
-  <si>
-    <t>surya.harahap93@yahoo.example</t>
-  </si>
-  <si>
-    <t>fitri.harahap242@outlook.example</t>
-  </si>
-  <si>
-    <t>hana.susanto763@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.hidayat911@yahoo.example</t>
-  </si>
-  <si>
-    <t>putri.tanjung36@gmial.example</t>
-  </si>
-  <si>
-    <t>putri.siregar5@yahoo.example</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.setiawan607@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.hakim536@outlook.example</t>
-  </si>
-  <si>
-    <t>eko.tanjung306.old@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.harahap839@yahoo.example</t>
-  </si>
-  <si>
-    <t>putri.lestari568@yahoo.example</t>
-  </si>
-  <si>
-    <t>hendra.gunawan940@gmail.example</t>
-  </si>
-  <si>
-    <t>rina.harahap48@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.nugroho155@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.setiawan655@outlook.example</t>
-  </si>
-  <si>
-    <t>hana.nugroho214@outlook.example</t>
-  </si>
-  <si>
-    <t>utami.rahayu707@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.sitompul456@outlook.example</t>
-  </si>
-  <si>
-    <t>gilang.halim475@outlook.example</t>
-  </si>
-  <si>
-    <t>budi.permana35@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.hakim372@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.santoso192@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.wibowo69@yahoo.example</t>
-  </si>
-  <si>
-    <t>joko.hakim562@outlook.example</t>
-  </si>
-  <si>
-    <t>wahyu.permana384@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.sitompul967@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.example</t>
-  </si>
-  <si>
-    <t>surya.wijaya733@yahoo.example</t>
-  </si>
-  <si>
-    <t>vina.susanto973@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.pratama94@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.sitompul744@outlook.example</t>
-  </si>
-  <si>
-    <t>tika.firmansyah424@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.nasution839@gmail.example</t>
-  </si>
-  <si>
-    <t>fajar.purnomo953@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.marpaung102@outlook.example</t>
-  </si>
-  <si>
-    <t>eko.marpaung525@yahoo.example</t>
-  </si>
-  <si>
-    <t>yuni.pratama110@outlook.example</t>
-  </si>
-  <si>
-    <t>gita.nugroho310@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.pratama295@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.hakim495@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.wijaya211@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.ramadhan266@yahoo.example</t>
-  </si>
-  <si>
-    <t>utami.lestari977.old@yahoo.example</t>
-  </si>
-  <si>
-    <t>gilang.purnomo421@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.rahayu567@outlook.example; indah.daeng923@outlook.example</t>
-  </si>
-  <si>
-    <t>gita.hidayat136@gmail.example</t>
-  </si>
-  <si>
-    <t>laras.pratama420@outlook.example</t>
-  </si>
-  <si>
-    <t>oki.marpaung169@yahoo.example</t>
-  </si>
-  <si>
-    <t>dimas.utomo981@yahoo.example</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.simanjuntak940@yahoo.example</t>
-  </si>
-  <si>
-    <t>nanda.setiawan155@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.gunawan950@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.santoso755@yahoo.example</t>
-  </si>
-  <si>
-    <t>gita.harahap701@outlook.example</t>
-  </si>
-  <si>
-    <t>wahyu.santoso947@outlook.example</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak295@yahoo.example</t>
-  </si>
-  <si>
-    <t>indah.sitompul761@outlook.example</t>
-  </si>
-  <si>
-    <t>gita.pane367@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.santoso493@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.hakim660@gmail.example</t>
-  </si>
-  <si>
-    <t>taufik.purnomo473@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.wijaya153@gmail.example</t>
-  </si>
-  <si>
-    <t>oki.harahap19@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.nugroho566@yahoo.example</t>
-  </si>
-  <si>
-    <t>wulan.ramadhan78@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.daeng504@yahoo.example</t>
-  </si>
-  <si>
-    <t>wulan.firmansyah542@yahoo.example</t>
-  </si>
-  <si>
-    <t>laras.harahap333@gmail.example</t>
-  </si>
-  <si>
-    <t>indah.simanjuntak489@gmail.example</t>
-  </si>
-  <si>
-    <t>budi.firmansyah122@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.saputra534@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.setiawan898@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.saputra601@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.lestari650@gmail.example</t>
-  </si>
-  <si>
-    <t>indah.santoso438@yahoo.example</t>
-  </si>
-  <si>
-    <t>mega.tanjung710@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.setiawan761@gmail.example</t>
-  </si>
-  <si>
-    <t>rina.halim222@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.purnomo689@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.saputra440@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.gunawan411@outlook.example</t>
-  </si>
-  <si>
-    <t>agus.gunawan88@outlook.example</t>
-  </si>
-  <si>
-    <t>joko.hakim589@outlook.example</t>
-  </si>
-  <si>
-    <t>tika.gunawan465@yahoo.example</t>
-  </si>
-  <si>
-    <t>bayu.simanjuntak308@yahoo.example</t>
-  </si>
-  <si>
-    <t>hana.sitompul434@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.wijaya532@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.firmansyah508@outlook.example</t>
-  </si>
-  <si>
-    <t>budi.rahayu406@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.permana924@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.example</t>
-  </si>
-  <si>
-    <t>putri.halim333@outlook.example</t>
-  </si>
-  <si>
-    <t>wulan.harahap781@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.pane11@yahoo.example</t>
-  </si>
-  <si>
-    <t>bayu.pane802@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.santoso953@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.rahayu804@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.tanjung401@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.lestari850@yahoo.example</t>
-  </si>
-  <si>
-    <t>agus.setiawan823@yahoo.example</t>
-  </si>
-  <si>
-    <t>wulan.halim37@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.susanto703@gmail.example</t>
-  </si>
-  <si>
-    <t>citra.gunawan898@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.harahap213@outlook.example</t>
-  </si>
-  <si>
-    <t>yuni.sitompul220@outlook.example</t>
-  </si>
-  <si>
-    <t>dimas.rahayu793@outlook.example</t>
-  </si>
-  <si>
-    <t>yuni.susanto823@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.gunawan937@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.wijaya940@outlook.example</t>
-  </si>
-  <si>
-    <t>sari.simanjuntak854@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.simanjuntak949@gmail.example</t>
-  </si>
-  <si>
-    <t>nanda.marpaung438@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.harahap1@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.sitompul616@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.susanto514@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.nugroho496@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.halim48@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.permana471@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.hidayat608@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.daeng276@gmail.example</t>
+    <t>7715211343</t>
+  </si>
+  <si>
+    <t>Taufik G******</t>
+  </si>
+  <si>
+    <t>Yuni S******</t>
+  </si>
+  <si>
+    <t>Putri W*****</t>
+  </si>
+  <si>
+    <t>Agus W*****</t>
+  </si>
+  <si>
+    <t>Dewi M*******</t>
+  </si>
+  <si>
+    <t>Bayu R*******</t>
+  </si>
+  <si>
+    <t>Mega H******</t>
+  </si>
+  <si>
+    <t>Budi T******</t>
+  </si>
+  <si>
+    <t>Budi N*******</t>
+  </si>
+  <si>
+    <t>Rina S******</t>
+  </si>
+  <si>
+    <t>Sari S******</t>
+  </si>
+  <si>
+    <t>Andi H******</t>
+  </si>
+  <si>
+    <t>Fajar T******</t>
+  </si>
+  <si>
+    <t>Sari S********</t>
+  </si>
+  <si>
+    <t>Budi G******</t>
+  </si>
+  <si>
+    <t>Lestari G******</t>
+  </si>
+  <si>
+    <t>Kartika P******</t>
+  </si>
+  <si>
+    <t>Zaki R*******</t>
+  </si>
+  <si>
+    <t>Utami P******</t>
+  </si>
+  <si>
+    <t>Agus S*******</t>
+  </si>
+  <si>
+    <t>Rizky K*****</t>
+  </si>
+  <si>
+    <t>Yoga H******</t>
+  </si>
+  <si>
+    <t>Hana M*******</t>
+  </si>
+  <si>
+    <t>Kartika S******</t>
+  </si>
+  <si>
+    <t>Fitri S********</t>
+  </si>
+  <si>
+    <t>Taufik H****</t>
+  </si>
+  <si>
+    <t>Maya N*******</t>
+  </si>
+  <si>
+    <t>Bayu P******</t>
+  </si>
+  <si>
+    <t>Maya S*******</t>
+  </si>
+  <si>
+    <t>Kartika P***</t>
+  </si>
+  <si>
+    <t>Budi S******</t>
+  </si>
+  <si>
+    <t>Nur K*****</t>
+  </si>
+  <si>
+    <t>Yuni P******</t>
+  </si>
+  <si>
+    <t>Hendra S******</t>
+  </si>
+  <si>
+    <t>Hendra P******</t>
+  </si>
+  <si>
+    <t>Fitri S**********</t>
+  </si>
+  <si>
+    <t>Oki M*******</t>
+  </si>
+  <si>
+    <t>Surya S*******</t>
+  </si>
+  <si>
+    <t>Taufik N******</t>
+  </si>
+  <si>
+    <t>Laras S******</t>
+  </si>
+  <si>
+    <t>Gita K*****</t>
+  </si>
+  <si>
+    <t>Zaki H****</t>
+  </si>
+  <si>
+    <t>Citra K*****</t>
+  </si>
+  <si>
+    <t>Hana U****</t>
+  </si>
+  <si>
+    <t>Rina T******</t>
+  </si>
+  <si>
+    <t>Andi N******</t>
+  </si>
+  <si>
+    <t>Agus H******</t>
+  </si>
+  <si>
+    <t>Wulan W*****</t>
+  </si>
+  <si>
+    <t>Rizky P******</t>
+  </si>
+  <si>
+    <t>Putri P***</t>
+  </si>
+  <si>
+    <t>Dewi N******</t>
+  </si>
+  <si>
+    <t>Hana R*******</t>
+  </si>
+  <si>
+    <t>Taufik U****</t>
+  </si>
+  <si>
+    <t>Joko S******</t>
+  </si>
+  <si>
+    <t>Irfan U****</t>
+  </si>
+  <si>
+    <t>Oki S******</t>
+  </si>
+  <si>
+    <t>Fajar P******</t>
+  </si>
+  <si>
+    <t>Indah P******</t>
+  </si>
+  <si>
+    <t>Putri P******</t>
+  </si>
+  <si>
+    <t>Surya S******</t>
+  </si>
+  <si>
+    <t>Mega S******</t>
+  </si>
+  <si>
+    <t>Putri N******</t>
+  </si>
+  <si>
+    <t>Vina P******</t>
+  </si>
+  <si>
+    <t>Vina K*****</t>
+  </si>
+  <si>
+    <t>Eko L******</t>
+  </si>
+  <si>
+    <t>Rina P******</t>
+  </si>
+  <si>
+    <t>Vina H****</t>
+  </si>
+  <si>
+    <t>Bayu S*******</t>
+  </si>
+  <si>
+    <t>Maya S******</t>
+  </si>
+  <si>
+    <t>Sari S*******</t>
+  </si>
+  <si>
+    <t>Eko P******</t>
+  </si>
+  <si>
+    <t>Andi R*******</t>
+  </si>
+  <si>
+    <t>Laras F*********</t>
+  </si>
+  <si>
+    <t>Wulan S**********</t>
+  </si>
+  <si>
+    <t>Tika R*******</t>
+  </si>
+  <si>
+    <t>Nanda H****</t>
+  </si>
+  <si>
+    <t>Bayu N*******</t>
+  </si>
+  <si>
+    <t>Andi S******</t>
+  </si>
+  <si>
+    <t>Dimas G******</t>
+  </si>
+  <si>
+    <t>Yoga S******</t>
+  </si>
+  <si>
+    <t>Gilang F*********</t>
+  </si>
+  <si>
+    <t>Agus T******</t>
+  </si>
+  <si>
+    <t>Gita S******</t>
+  </si>
+  <si>
+    <t>Fitri T******</t>
+  </si>
+  <si>
+    <t>Vina D****</t>
+  </si>
+  <si>
+    <t>Tika S******</t>
+  </si>
+  <si>
+    <t>Putri S******</t>
+  </si>
+  <si>
+    <t>Lestari P******</t>
+  </si>
+  <si>
+    <t>Joko W*****</t>
+  </si>
+  <si>
+    <t>Vina L******</t>
+  </si>
+  <si>
+    <t>Joko S*******</t>
+  </si>
+  <si>
+    <t>Oki R*****</t>
+  </si>
+  <si>
+    <t>Sari T******</t>
+  </si>
+  <si>
+    <t>Rizky S******</t>
+  </si>
+  <si>
+    <t>Surya G******</t>
+  </si>
+  <si>
+    <t>Eko S*******</t>
+  </si>
+  <si>
+    <t>Bayu U****</t>
+  </si>
+  <si>
+    <t>Sari W*****</t>
+  </si>
+  <si>
+    <t>Kartika N******</t>
+  </si>
+  <si>
+    <t>Gilang H******</t>
+  </si>
+  <si>
+    <t>Hendra G******</t>
+  </si>
+  <si>
+    <t>Dimas U****</t>
+  </si>
+  <si>
+    <t>Kartika K*****</t>
+  </si>
+  <si>
+    <t>Maya P******</t>
+  </si>
+  <si>
+    <t>Kartika H******</t>
+  </si>
+  <si>
+    <t>Citra H****</t>
+  </si>
+  <si>
+    <t>Yoga H****</t>
+  </si>
+  <si>
+    <t>Fitri S******</t>
+  </si>
+  <si>
+    <t>Budi H******</t>
+  </si>
+  <si>
+    <t>Gita P***</t>
+  </si>
+  <si>
+    <t>Dimas P******</t>
+  </si>
+  <si>
+    <t>Wahyu D****</t>
+  </si>
+  <si>
+    <t>Rahmat T******</t>
+  </si>
+  <si>
+    <t>Utami S******</t>
+  </si>
+  <si>
+    <t>Citra P******</t>
+  </si>
+  <si>
+    <t>Hendra W*****</t>
+  </si>
+  <si>
+    <t>Fajar L******</t>
+  </si>
+  <si>
+    <t>Budi S*******</t>
+  </si>
+  <si>
+    <t>Utami T******</t>
+  </si>
+  <si>
+    <t>Hendra R*******</t>
+  </si>
+  <si>
+    <t>Joko U****</t>
+  </si>
+  <si>
+    <t>Joko L******</t>
+  </si>
+  <si>
+    <t>Yuni W*****</t>
+  </si>
+  <si>
+    <t>Rahmat S**********</t>
+  </si>
+  <si>
+    <t>Laras N*******</t>
+  </si>
+  <si>
+    <t>Wahyu H****</t>
+  </si>
+  <si>
+    <t>Surya P******</t>
+  </si>
+  <si>
+    <t>Citra L******</t>
+  </si>
+  <si>
+    <t>Hana S******</t>
+  </si>
+  <si>
+    <t>Rina H******</t>
+  </si>
+  <si>
+    <t>Mega K*****</t>
+  </si>
+  <si>
+    <t>Wulan R*******</t>
+  </si>
+  <si>
+    <t>Putri R*******</t>
+  </si>
+  <si>
+    <t>customer.0766@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0366@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0183@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0856@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0300@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0757@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0228@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0065@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0802@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0280@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0892@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0880@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0515@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0471@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0882@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0561@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0125@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0482@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0603@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0742@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0509@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0497@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0270@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0890@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0175@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0884@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0381@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0355@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0676@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0737@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0404@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0562@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0070@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0885@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0739@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0197@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0284@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0820@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0068@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0811@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0061@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0552@gmail.example; customer.0420@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0245@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0543@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0007@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0883@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0732@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0709@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0403@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0735@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0360@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0557@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0369@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0897@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0406@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0765@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0432@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0483@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0195@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0473@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0198@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0091@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0756@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0151@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0340@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0392@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0572@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0265@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0190@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0383@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0176@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0821@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0869@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0590@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0530@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0124@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0663.old@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0702@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0491@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0025@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0348@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0193@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0148@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0614@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0314@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0640@gmial.example</t>
+  </si>
+  <si>
+    <t>customer.0857@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0074@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0645@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0058@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0127@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0865@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0384@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0203@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0248@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0139@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0417@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0028@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0706@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0073@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0607@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0830@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0496@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0252@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0718@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0714@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0032@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0337@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0405@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0330@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0323@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0375@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0460@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0243@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0478@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0385@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0745@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0418@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0338@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0681@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0054@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0746@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0002@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0031@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0047@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0889@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0332@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0349@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0256@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0063@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0733@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0122@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0269@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0708@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0116@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0419@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0097@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0237@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0687@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0611@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0037@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0537@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0439@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0489@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0799@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0620@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0710@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0423@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0059@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0698@gmail.example</t>
+  </si>
+  <si>
+    <t>SBY</t>
+  </si>
+  <si>
+    <t>JKT</t>
+  </si>
+  <si>
+    <t>BDG</t>
+  </si>
+  <si>
+    <t>MKS</t>
+  </si>
+  <si>
+    <t>YGY</t>
   </si>
   <si>
     <t>MDN</t>
   </si>
   <si>
-    <t>JKT</t>
-  </si>
-  <si>
-    <t>BDG</t>
-  </si>
-  <si>
-    <t>MKS</t>
-  </si>
-  <si>
-    <t>YGY</t>
-  </si>
-  <si>
-    <t>SBY</t>
+    <t>MATURITY</t>
   </si>
   <si>
     <t>BENEFIT_PAYMENT</t>
   </si>
   <si>
-    <t>MATURITY</t>
-  </si>
-  <si>
     <t>REINSTATEMENT</t>
   </si>
   <si>
-    <t>jkt.staff@gmail.example</t>
+    <t>bdg.staff@gmail.example</t>
   </si>
 </sst>
 </file>
@@ -1765,13 +1735,13 @@
         <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F2" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1785,13 +1755,13 @@
         <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E3" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1805,13 +1775,13 @@
         <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F4" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1825,13 +1795,13 @@
         <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E5" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1845,13 +1815,13 @@
         <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E6" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F6" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1865,13 +1835,13 @@
         <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E7" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F7" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1885,13 +1855,13 @@
         <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E8" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F8" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1905,13 +1875,13 @@
         <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E9" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F9" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1925,13 +1895,13 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F10" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1945,13 +1915,13 @@
         <v>167</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F11" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1965,13 +1935,13 @@
         <v>168</v>
       </c>
       <c r="D12" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E12" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F12" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1985,13 +1955,13 @@
         <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E13" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F13" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2005,13 +1975,13 @@
         <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E14" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F14" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2025,13 +1995,13 @@
         <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E15" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F15" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2045,13 +2015,13 @@
         <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E16" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F16" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2065,13 +2035,13 @@
         <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E17" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F17" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2085,13 +2055,13 @@
         <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E18" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F18" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2105,13 +2075,13 @@
         <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="E19" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F19" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2125,13 +2095,13 @@
         <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E20" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F20" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2145,13 +2115,13 @@
         <v>177</v>
       </c>
       <c r="D21" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="E21" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F21" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2162,16 +2132,16 @@
         <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E22" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="F22" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2182,16 +2152,16 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E23" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F23" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2202,16 +2172,16 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E24" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F24" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2222,16 +2192,16 @@
         <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D25" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E25" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F25" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2242,16 +2212,16 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F26" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2262,16 +2232,16 @@
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D27" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="E27" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F27" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2282,16 +2252,16 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E28" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F28" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2302,16 +2272,16 @@
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E29" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F29" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2322,16 +2292,16 @@
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E30" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F30" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2342,16 +2312,16 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D31" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E31" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F31" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2362,16 +2332,16 @@
         <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D32" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E32" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F32" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2382,16 +2352,16 @@
         <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E33" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F33" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2402,16 +2372,16 @@
         <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D34" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E34" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F34" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2422,16 +2392,16 @@
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D35" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E35" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F35" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2442,16 +2412,16 @@
         <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D36" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E36" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F36" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2462,16 +2432,16 @@
         <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E37" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F37" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2482,16 +2452,16 @@
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D38" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E38" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F38" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2502,16 +2472,16 @@
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E39" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2522,16 +2492,16 @@
         <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D40" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E40" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F40" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2542,16 +2512,16 @@
         <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D41" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E41" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F41" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2562,16 +2532,16 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D42" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E42" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F42" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2582,16 +2552,16 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E43" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F43" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2602,16 +2572,16 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E44" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F44" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2622,16 +2592,16 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D45" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E45" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F45" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2642,16 +2612,16 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E46" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F46" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2662,16 +2632,16 @@
         <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E47" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F47" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2682,19 +2652,19 @@
         <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D48" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E48" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F48" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -2702,19 +2672,19 @@
         <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D49" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E49" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F49" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2722,19 +2692,19 @@
         <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D50" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E50" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F50" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2742,19 +2712,19 @@
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D51" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E51" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F51" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2762,19 +2732,19 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D52" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E52" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F52" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2782,19 +2752,19 @@
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="D53" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E53" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F53" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2802,19 +2772,19 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D54" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E54" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F54" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2822,19 +2792,19 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D55" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E55" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F55" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2842,19 +2812,19 @@
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="D56" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E56" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F56" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2862,19 +2832,19 @@
         <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E57" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F57" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2882,19 +2852,19 @@
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D58" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E58" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F58" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2902,19 +2872,19 @@
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D59" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E59" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F59" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -2922,19 +2892,19 @@
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E60" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F60" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -2942,22 +2912,19 @@
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D61" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E61" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F61" t="s">
-        <v>459</v>
-      </c>
-      <c r="G61" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -2965,19 +2932,19 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D62" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E62" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F62" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -2985,19 +2952,19 @@
         <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D63" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E63" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F63" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -3005,19 +2972,19 @@
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D64" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E64" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F64" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -3025,19 +2992,19 @@
         <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D65" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E65" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F65" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -3045,19 +3012,19 @@
         <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E66" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F66" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -3065,19 +3032,19 @@
         <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D67" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E67" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F67" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -3085,19 +3052,19 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D68" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E68" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F68" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -3105,19 +3072,22 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D69" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E69" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F69" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>449</v>
+      </c>
+      <c r="G69" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -3125,19 +3095,19 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E70" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F70" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -3145,19 +3115,19 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D71" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E71" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F71" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -3165,19 +3135,19 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E72" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F72" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -3185,19 +3155,19 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D73" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="E73" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F73" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -3205,19 +3175,19 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D74" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E74" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F74" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -3225,19 +3195,19 @@
         <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D75" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E75" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F75" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -3245,19 +3215,19 @@
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D76" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E76" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F76" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -3265,19 +3235,19 @@
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D77" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E77" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F77" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -3285,19 +3255,19 @@
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D78" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E78" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="F78" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>7</v>
       </c>
@@ -3305,19 +3275,19 @@
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D79" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E79" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F79" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>7</v>
       </c>
@@ -3325,16 +3295,16 @@
         <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D80" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E80" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F80" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3345,16 +3315,16 @@
         <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D81" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E81" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F81" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3365,16 +3335,16 @@
         <v>88</v>
       </c>
       <c r="C82" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D82" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E82" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F82" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3385,16 +3355,16 @@
         <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D83" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E83" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="F83" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3405,16 +3375,16 @@
         <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D84" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="E84" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F84" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3425,16 +3395,16 @@
         <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="D85" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E85" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F85" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3445,16 +3415,16 @@
         <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D86" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="E86" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F86" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3465,16 +3435,16 @@
         <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="D87" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E87" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F87" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3485,16 +3455,16 @@
         <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D88" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E88" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F88" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3505,16 +3475,16 @@
         <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D89" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E89" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F89" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3525,16 +3495,16 @@
         <v>96</v>
       </c>
       <c r="C90" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D90" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="E90" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F90" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3545,16 +3515,16 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D91" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E91" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F91" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3565,16 +3535,16 @@
         <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D92" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="E92" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F92" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3585,16 +3555,16 @@
         <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="D93" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E93" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F93" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3605,16 +3575,16 @@
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D94" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E94" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F94" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3625,16 +3595,16 @@
         <v>101</v>
       </c>
       <c r="C95" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D95" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E95" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F95" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3645,16 +3615,16 @@
         <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D96" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E96" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F96" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3665,16 +3635,16 @@
         <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D97" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E97" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F97" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3685,16 +3655,16 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D98" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E98" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F98" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3705,16 +3675,16 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D99" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="E99" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F99" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3725,16 +3695,16 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D100" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E100" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F100" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3745,16 +3715,16 @@
         <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D101" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E101" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F101" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3765,16 +3735,16 @@
         <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D102" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E102" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F102" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3785,16 +3755,16 @@
         <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D103" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E103" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F103" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3805,16 +3775,16 @@
         <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D104" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="E104" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F104" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3825,16 +3795,16 @@
         <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E105" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F105" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3845,16 +3815,16 @@
         <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D106" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E106" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F106" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3865,16 +3835,16 @@
         <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="D107" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E107" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F107" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3885,16 +3855,16 @@
         <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="D108" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="E108" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F108" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3905,16 +3875,16 @@
         <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D109" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="E109" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F109" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3925,16 +3895,16 @@
         <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D110" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E110" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F110" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3945,16 +3915,16 @@
         <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D111" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="E111" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F111" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3965,16 +3935,16 @@
         <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D112" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E112" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F112" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3985,16 +3955,16 @@
         <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E113" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F113" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4005,16 +3975,16 @@
         <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="D114" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="E114" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F114" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4025,16 +3995,16 @@
         <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E115" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F115" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4045,16 +4015,16 @@
         <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D116" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="E116" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F116" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4065,16 +4035,16 @@
         <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E117" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F117" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4085,16 +4055,16 @@
         <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="D118" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="E118" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F118" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4105,16 +4075,16 @@
         <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E119" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F119" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4125,16 +4095,16 @@
         <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D120" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="E120" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F120" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4145,16 +4115,16 @@
         <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="D121" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="E121" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F121" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4165,16 +4135,16 @@
         <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="D122" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="E122" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F122" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4185,16 +4155,16 @@
         <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E123" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F123" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4205,16 +4175,16 @@
         <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E124" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F124" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4225,16 +4195,16 @@
         <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="D125" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E125" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F125" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4245,16 +4215,16 @@
         <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="E126" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F126" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4265,16 +4235,16 @@
         <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E127" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F127" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4285,16 +4255,16 @@
         <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D128" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="E128" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F128" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4305,16 +4275,16 @@
         <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="E129" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F129" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4325,16 +4295,16 @@
         <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D130" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="E130" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F130" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4345,16 +4315,16 @@
         <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D131" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="E131" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F131" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4365,16 +4335,16 @@
         <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D132" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="E132" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F132" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4385,16 +4355,16 @@
         <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D133" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E133" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F133" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4405,16 +4375,16 @@
         <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D134" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E134" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F134" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4425,16 +4395,16 @@
         <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D135" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="E135" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F135" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4445,16 +4415,16 @@
         <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D136" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="E136" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F136" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4465,16 +4435,16 @@
         <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D137" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E137" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F137" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4485,16 +4455,16 @@
         <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D138" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="E138" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F138" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4505,16 +4475,16 @@
         <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D139" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="E139" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F139" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4525,16 +4495,16 @@
         <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D140" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="E140" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F140" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4545,16 +4515,16 @@
         <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D141" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="E141" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F141" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4565,16 +4535,16 @@
         <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D142" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="E142" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F142" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4585,16 +4555,16 @@
         <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="D143" t="s">
+        <v>432</v>
+      </c>
+      <c r="E143" t="s">
         <v>442</v>
       </c>
-      <c r="E143" t="s">
-        <v>453</v>
-      </c>
       <c r="F143" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4605,16 +4575,16 @@
         <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D144" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="E144" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F144" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4625,16 +4595,16 @@
         <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D145" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E145" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F145" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4645,16 +4615,16 @@
         <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D146" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="E146" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F146" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4665,16 +4635,16 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D147" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E147" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F147" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4685,16 +4655,16 @@
         <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="D148" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="E148" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F148" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4705,16 +4675,16 @@
         <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="D149" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="E149" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F149" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4725,16 +4695,16 @@
         <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D150" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E150" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F150" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4745,16 +4715,16 @@
         <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D151" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="E151" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F151" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
